--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/abr-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/abr-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC abr-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC abr-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/abr-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/abr-2026.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Penco - Salud</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES Y CONTROL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Administración Central</t>
+          <t>CORP.MUNICIPAL GABRIEL GONZALEZ VIDELA DE LA SERENA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SAMU</t>
+          <t>Centro Metropolitano de Atención Prehospitalaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Instituto de Seguridad Laboral</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/abr-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/abr-2026.xlsx
@@ -562,7 +562,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +944,11 @@
           <t>76.981.642-9</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1070,11 @@
           <t>76.486.150-7</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1196,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1261,11 @@
           <t>76.334.381-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1326,11 @@
           <t>77.553.790-6</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1452,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1517,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1582,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1725,7 +1773,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1786,7 +1838,11 @@
           <t>76.334.381-2</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1847,7 +1903,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1908,7 +1968,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1969,7 +2033,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2030,7 +2098,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2091,7 +2163,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2213,7 +2289,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2274,7 +2354,11 @@
           <t>92.580.000-7</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2335,7 +2419,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2457,7 +2545,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2579,7 +2671,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2640,7 +2736,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2701,7 +2801,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2762,7 +2866,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2823,7 +2931,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2884,7 +2996,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2945,7 +3061,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3006,7 +3126,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3067,7 +3191,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3128,7 +3256,11 @@
           <t>76.981.642-9</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3254,7 +3386,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3376,7 +3512,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3437,7 +3577,11 @@
           <t>77.553.790-6</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3498,7 +3642,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3559,7 +3707,11 @@
           <t>76.981.642-9</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3620,7 +3772,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3681,7 +3837,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3742,7 +3902,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/abr-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/abr-2026.xlsx
@@ -1042,7 +1042,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
